--- a/data/single_run/input/components/facilities/facilities_meisner.xlsx
+++ b/data/single_run/input/components/facilities/facilities_meisner.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,33 +425,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>facility_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>c2_up_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>unload_policy</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>load_policy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>x_km</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>y_km</t>
         </is>
       </c>
     </row>
@@ -469,6 +491,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +524,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +557,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +590,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +623,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +656,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +689,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +722,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +755,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +788,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +821,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +854,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +887,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +920,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +953,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -874,6 +986,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -901,6 +1019,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>51</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +1052,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1085,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1118,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,6 +1151,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1036,6 +1184,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>63</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1063,6 +1217,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>69</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1090,6 +1250,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>69</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1117,6 +1283,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>75</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1144,6 +1316,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1171,6 +1349,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>81</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1198,6 +1382,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>81</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1225,6 +1415,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>87</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1252,6 +1448,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>87</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1275,6 +1477,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1298,6 +1506,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F33" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1321,6 +1535,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F34" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1344,6 +1564,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F35" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1367,6 +1593,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1390,6 +1622,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1413,6 +1651,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1436,6 +1680,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="G39" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1459,6 +1709,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F40" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="G40" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1482,6 +1738,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="G41" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1505,6 +1767,12 @@
           <t>load_planned</t>
         </is>
       </c>
+      <c r="F42" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1527,6 +1795,12 @@
         <is>
           <t>load_planned</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="G43" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/single_run/input/components/facilities/facilities_meisner.xlsx
+++ b/data/single_run/input/components/facilities/facilities_meisner.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>facility_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>c2_up_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>unload_policy</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>load_policy</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>x_km</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>y_km</t>
         </is>
@@ -492,7 +480,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -525,7 +513,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
@@ -558,7 +546,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>7</v>
@@ -624,7 +612,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -657,7 +645,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>7</v>
@@ -690,7 +678,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
@@ -723,7 +711,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>7</v>
@@ -756,7 +744,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -789,7 +777,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
@@ -822,7 +810,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
@@ -855,7 +843,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -888,7 +876,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
@@ -921,7 +909,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
         <v>7</v>
@@ -954,7 +942,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
         <v>4</v>
@@ -987,7 +975,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
         <v>7</v>
@@ -1020,7 +1008,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G18" t="n">
         <v>4</v>
@@ -1053,7 +1041,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G19" t="n">
         <v>7</v>
@@ -1062,19 +1050,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ccp_10</t>
+          <t>r2_1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1086,28 +1070,24 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>r2_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1119,28 +1099,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ccp_11</t>
+          <t>r2_3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1152,28 +1128,24 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>r2_4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1185,28 +1157,24 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ccp_12</t>
+          <t>r2_5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1218,28 +1186,24 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>r2_6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1251,28 +1215,24 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ccp_13</t>
+          <t>r2_7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1284,28 +1244,24 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>r2_8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1320,25 +1276,21 @@
         <v>75</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ccp_14</t>
+          <t>r2_9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
+          <t>Role2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>unload_planned</t>
@@ -1350,456 +1302,9 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>r1_14</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>81</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ccp_15</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>C2_CCP_R1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>87</v>
-      </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>C2_R1_R2</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>87</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>r2_1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="G32" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>r2_2</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="G33" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>r2_3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="G34" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>r2_4</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="G35" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>r2_5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="G36" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>r2_6</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="G37" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>r2_7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="G38" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>r2_8</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="G39" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>r2_9</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="G40" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>r2_10</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="G41" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>r2_11</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="G42" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>r2_12</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Role2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>unload_planned</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>load_planned</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="G43" t="n">
         <v>15</v>
       </c>
     </row>
